--- a/annotation_batch.xlsx
+++ b/annotation_batch.xlsx
@@ -518,7 +518,11 @@
           <t>{"display": "Positive", "storage space": "Positive"}</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
     </row>
@@ -546,10 +550,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>{"key size": "Positive", "letter size": "Positive", "return": "Positive"}</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -574,7 +582,11 @@
           <t>{"lightning connector": "Negative", "connector": "Negative", "dock": "Negative", "usb port": "Negative", "charging": "Negative", "dock connector": "Negative"}</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -626,7 +638,11 @@
           <t>{"screen": "Negative", "installed": "Negative", "colors": "Negative"}</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -652,7 +668,11 @@
           <t>{"iphone": "Neutral", "firmware": "Negative"}</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -756,7 +776,11 @@
           <t>{"windows": "Neutral", "audio": "Negative"}</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -812,7 +836,11 @@
           <t>{"stock": "Negative", "communication": "Positive", "price": "Positive"}</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -919,7 +947,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>{"charging": "Negative", "usbports": "Negative", "price": "Negative"}</t>
+          <t>{"cover": "Positive", "material": "Positive"}</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -998,7 +1026,11 @@
           <t>{"construction": "Neutral", "fit": "Negative"}</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1024,7 +1056,11 @@
           <t>{"connectivity": "Positive", "usb": "Positive", "- in bluetooth": "Positive", "setup": "Positive", "sound quality": "Positive", "portability": "Positive"}</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1050,7 +1086,11 @@
           <t>{"windows 8": "Negative", "windows 7": "Neutral", "windows 8 \" app": "Negative", "picture quality": "Negative"}</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1076,7 +1116,11 @@
           <t>{"price": "Negative", "wait": "Negative", "sound": "Neutral"}</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1102,7 +1146,11 @@
           <t>{"flip": "Positive", "hdmi port": "Positive", "works": "Positive"}</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1180,7 +1228,11 @@
           <t>{"driver installation": "Positive", "d - link drivers": "Negative", "intel wireless": "Negative", "internal wireless card": "Negative", "windows": "Neutral"}</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1258,7 +1310,11 @@
           <t>{"sound quality": "Positive", "earhooks": "Positive"}</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1312,10 +1368,14 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>{"cover": "Negative"}</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
@@ -1343,7 +1403,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>{"price": "Negative"}</t>
+          <t>{"price": "Positive", "internet": "Negative"}</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -1370,8 +1430,16 @@
           <t>{"priced": "Positive", "camera": "Negative", "charging cable": "Positive", "camera adapters": "Negative", "jail": "Negative"}</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>{"clip": "Negative"}</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
@@ -1396,7 +1464,11 @@
           <t>{"plug in base": "Positive", "case": "Negative", "connection": "Negative", "cord": "Negative", "usb": "Neutral", "cable": "Negative"}</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1474,7 +1546,11 @@
           <t>{"screen protector": "Negative", "screen": "Negative", "charger": "Positive", "chord": "Negative"}</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1500,7 +1576,11 @@
           <t>{"screen": "Neutral", "external keyboard": "Neutral", "docking station": "Positive", "software": "Positive"}</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1552,8 +1632,16 @@
           <t>{"webcam": "Negative", "windows 7": "Negative"}</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>{"webcam": "Positive"}</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
@@ -1656,7 +1744,11 @@
           <t>{"sound": "Negative"}</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1760,7 +1852,11 @@
           <t>{"charge": "Negative"}</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -1786,7 +1882,11 @@
           <t>{"price": "Neutral", "- ear": "Positive"}</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -1864,7 +1964,11 @@
           <t>{"glass": "Negative", "fan": "Negative", "usb port": "Negative", "main board": "Negative"}</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -1942,7 +2046,11 @@
           <t>{"adhesive": "Negative", "lense": "Negative"}</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1994,7 +2102,11 @@
           <t>{"browser": "Negative", "rom": "Positive"}</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2023,7 +2135,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>{"weight": "Positive", "storage": "Positive", "resolution": "Positive"}</t>
+          <t>{"price": "Neutral", "baterry": "Positive", "zoom": "Negative", "carry": "Positive"}</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -2076,7 +2188,11 @@
           <t>{"keyboard": "Positive", "system": "Negative", "ergonomic mouse": "Negative"}</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -2388,7 +2504,11 @@
         </is>
       </c>
       <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2440,7 +2560,11 @@
           <t>{"charge": "Positive", "battery": "Negative"}</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2466,7 +2590,11 @@
           <t>{"quality": "Negative", "plastic": "Negative", "case": "Negative", "lock slot": "Negative", "headphone jack": "Negative", "cover": "Negative"}</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2492,7 +2620,11 @@
           <t>{"storage": "Negative", "windows": "Neutral", "nslu2": "Positive"}</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2518,7 +2650,11 @@
           <t>{"built - in camera": "Negative", "picture": "Positive", "sound": "Positive"}</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2730,8 +2866,16 @@
           <t>{"coby": "Negative", "boot": "Negative"}</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
-      <c r="G87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>{"return": "Positive"}</t>
+        </is>
+      </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
@@ -2782,7 +2926,11 @@
           <t>{"usb ports": "Neutral", "usb 3 . 0 ports": "Negative", "hub": "Positive"}</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -2834,7 +2982,11 @@
           <t>{"battery": "Negative", "power chord": "Negative", "return": "Negative"}</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -2990,7 +3142,11 @@
           <t>{"delivery": "Positive", "battery": "Positive"}</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -3068,7 +3224,11 @@
           <t>{"filters": "Positive", "filter": "Positive", "holder": "Negative"}</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -3123,7 +3283,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>{"storage": "Negative"}</t>
+          <t>{"memory": "Positive"}</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
@@ -3150,7 +3310,11 @@
           <t>{"disc": "Negative", "windows xp": "Negative", "vista": "Negative", "windows server 2033": "Negative", "blu ray system": "Negative", "windows 7": "Negative", "support": "Negative", "emailed": "Negative", "wireless adaptor": "Negative", "sound": "Negative"}</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="inlineStr"/>
     </row>
@@ -3202,8 +3366,16 @@
           <t>{"kindle": "Negative"}</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>{"case": "Negative"}</t>
+        </is>
+      </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
@@ -3254,7 +3426,11 @@
           <t>{"screen": "Positive", "protector": "Negative"}</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>no_aspect</t>
+        </is>
+      </c>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3306,7 +3482,11 @@
           <t>{"buds": "Negative", "ear pieces": "Negative", "bud": "Negative", "wiring": "Negative"}</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3332,7 +3512,11 @@
           <t>{"case": "Positive", "fit tablet": "Positive", "color": "Positive"}</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -3360,10 +3544,14 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>{"battery": "Negative"}</t>
+        </is>
+      </c>
       <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
@@ -3442,10 +3630,14 @@
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr"/>
+          <t>missed_all</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>{"battery": "Positive", "touchpad": "Positive", "microphone": "Positive", "internet": "Negative"}</t>
+        </is>
+      </c>
       <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
@@ -3551,7 +3743,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>{"price": "Positive", "battery": "Positive"}</t>
+          <t>{"price": "Positive", "battery": "Positive", "shipping": "Positive"}</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
@@ -3628,14 +3820,10 @@
       <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>missed_all</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>{"cooling": "Negative"}</t>
-        </is>
-      </c>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
@@ -3660,7 +3848,11 @@
           <t>{"cord": "Negative", "base": "Negative", "works": "Negative"}</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -3764,7 +3956,11 @@
           <t>{"cable": "Negative"}</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -3920,7 +4116,11 @@
           <t>{"fits": "Positive", "buttons": "Positive", "screen": "Positive", "screen protector": "Negative", "headphone jack": "Negative", "micro usb": "Negative", "hdmi port": "Negative", "ports": "Negative", "jack": "Negative", "micro usb port": "Negative"}</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr"/>
     </row>
@@ -3998,7 +4198,11 @@
           <t>{"sound": "Negative"}</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -4102,7 +4306,11 @@
           <t>{"modem": "Negative"}</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -4180,7 +4388,11 @@
           <t>{"speakers": "Negative", "design": "Positive", "volume": "Negative"}</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -4258,7 +4470,11 @@
           <t>{"windows 7": "Neutral", "motherboard": "Positive", "software": "Positive", "os": "Neutral"}</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -4284,7 +4500,11 @@
           <t>{"material": "Neutral", "velcro": "Neutral"}</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -4388,7 +4608,11 @@
           <t>{"price": "Negative"}</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -4440,7 +4664,11 @@
           <t>{"frequency": "Neutral"}</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr"/>
     </row>
@@ -4518,7 +4746,11 @@
           <t>{"power port": "Negative", "center console": "Negative", "microphone": "Negative"}</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -4546,7 +4778,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>correct</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="G156" t="inlineStr"/>
@@ -4574,8 +4806,16 @@
           <t>{"ipad": "Neutral"}</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>{"protection": "Positive"}</t>
+        </is>
+      </c>
       <c r="H157" t="inlineStr"/>
     </row>
     <row r="158">
@@ -4652,7 +4892,11 @@
           <t>{"adhesive": "Positive", "cables": "Positive", "install": "Negative", "installation": "Positive"}</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -4782,7 +5026,11 @@
           <t>{"case": "Positive", "color": "Negative"}</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr"/>
     </row>
@@ -4834,8 +5082,16 @@
           <t>{"bass": "Negative", "logitech": "Negative"}</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr"/>
-      <c r="G167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>{"bass": "Positive"}</t>
+        </is>
+      </c>
       <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
@@ -5016,7 +5272,11 @@
           <t>{"external recorder": "Positive", "external digital recorder": "Positive"}</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr"/>
     </row>
@@ -5042,7 +5302,11 @@
           <t>{"construction": "Negative", "plastic post": "Negative", "power connector": "Negative", "plug": "Negative", "wires": "Negative", "enclosure": "Negative"}</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
     </row>
@@ -5092,10 +5356,14 @@
       <c r="E177" t="inlineStr"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr"/>
+          <t>missed_all</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>{"quality": "Negative"}</t>
+        </is>
+      </c>
       <c r="H177" t="inlineStr"/>
     </row>
     <row r="178">
@@ -5196,10 +5464,14 @@
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr">
         <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr"/>
+          <t>missed_all</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>{"case": "Negative"}</t>
+        </is>
+      </c>
       <c r="H181" t="inlineStr"/>
     </row>
     <row r="182">
@@ -5250,7 +5522,11 @@
           <t>{"graphics tablets": "Neutral", "drivers": "Neutral", "windows 8": "Neutral", "windows 8 . 1": "Negative", "service": "Negative", "system restore": "Neutral", "cd drivers": "Neutral", "compatibility mode": "Neutral"}</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr"/>
     </row>
@@ -5302,7 +5578,11 @@
           <t>{"inputs": "Negative", "input": "Negative", "quality": "Positive"}</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
     </row>
@@ -5352,10 +5632,14 @@
       <c r="E187" t="inlineStr"/>
       <c r="F187" t="inlineStr">
         <is>
-          <t>correct</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr"/>
+          <t>missed_all</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>{"camera": "Positive"}</t>
+        </is>
+      </c>
       <c r="H187" t="inlineStr"/>
     </row>
     <row r="188">
@@ -5406,7 +5690,11 @@
           <t>{"cover": "Positive", "screen": "Neutral"}</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr"/>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr"/>
     </row>
@@ -5432,7 +5720,11 @@
           <t>{"pricing": "Positive"}</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr"/>
     </row>
@@ -5484,7 +5776,11 @@
           <t>{"quality": "Positive", "software": "Negative", "feature": "Negative", "height": "Negative", "buttons": "Negative"}</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr"/>
     </row>
@@ -5536,7 +5832,11 @@
           <t>{"weight": "Positive", "tip": "Positive", "clip": "Negative", "base": "Negative"}</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr"/>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr"/>
     </row>
@@ -5614,7 +5914,11 @@
           <t>{"card reader": "Negative", "plastics": "Negative", "usb": "Negative", "micro usb ports": "Negative", "usb ports": "Negative", "sd slot": "Negative", "usb hub": "Negative", "card": "Negative"}</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr"/>
     </row>
@@ -5640,7 +5944,11 @@
           <t>{"reception": "Negative", "usb port": "Negative", "display": "Negative"}</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr"/>
     </row>
@@ -5692,7 +6000,11 @@
           <t>{"key": "Negative", "software": "Negative", "keyboard": "Negative", "cost": "Negative"}</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr"/>
     </row>
@@ -5718,7 +6030,11 @@
           <t>{"subwoofer": "Negative", "features": "Positive", "subwoofer hum": "Negative"}</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr"/>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr"/>
     </row>
